--- a/artfynd/A 33687-2025 artfynd.xlsx
+++ b/artfynd/A 33687-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127110801</v>
       </c>
       <c r="B2" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,50 +794,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127110780</v>
+        <v>127111075</v>
       </c>
       <c r="B3" t="n">
-        <v>98361</v>
+        <v>57817</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -845,13 +841,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578475</v>
+        <v>578460</v>
       </c>
       <c r="R3" t="n">
-        <v>6406034</v>
+        <v>6406044</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -889,7 +885,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -908,46 +903,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127111075</v>
+        <v>127110780</v>
       </c>
       <c r="B4" t="n">
-        <v>57817</v>
+        <v>98436</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -955,13 +954,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578460</v>
+        <v>578475</v>
       </c>
       <c r="R4" t="n">
-        <v>6406044</v>
+        <v>6406034</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,6 +998,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1020,7 +1020,7 @@
         <v>127110856</v>
       </c>
       <c r="B5" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>127110820</v>
       </c>
       <c r="B6" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 33687-2025 artfynd.xlsx
+++ b/artfynd/A 33687-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127110801</v>
       </c>
       <c r="B2" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,46 +794,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127111075</v>
+        <v>127110780</v>
       </c>
       <c r="B3" t="n">
-        <v>57817</v>
+        <v>98442</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -841,13 +845,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578460</v>
+        <v>578475</v>
       </c>
       <c r="R3" t="n">
-        <v>6406044</v>
+        <v>6406034</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,6 +889,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -903,50 +908,46 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127110780</v>
+        <v>127111075</v>
       </c>
       <c r="B4" t="n">
-        <v>98436</v>
+        <v>57817</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -954,13 +955,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578475</v>
+        <v>578460</v>
       </c>
       <c r="R4" t="n">
-        <v>6406034</v>
+        <v>6406044</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -998,7 +999,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1020,7 +1020,7 @@
         <v>127110856</v>
       </c>
       <c r="B5" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>127110820</v>
       </c>
       <c r="B6" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 33687-2025 artfynd.xlsx
+++ b/artfynd/A 33687-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127110801</v>
       </c>
       <c r="B2" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>127110780</v>
       </c>
       <c r="B3" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>127110856</v>
       </c>
       <c r="B5" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>127110820</v>
       </c>
       <c r="B6" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 33687-2025 artfynd.xlsx
+++ b/artfynd/A 33687-2025 artfynd.xlsx
@@ -794,50 +794,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127110780</v>
+        <v>127111075</v>
       </c>
       <c r="B3" t="n">
-        <v>98443</v>
+        <v>57817</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -845,13 +841,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578475</v>
+        <v>578460</v>
       </c>
       <c r="R3" t="n">
-        <v>6406034</v>
+        <v>6406044</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -889,7 +885,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -908,46 +903,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127111075</v>
+        <v>127110780</v>
       </c>
       <c r="B4" t="n">
-        <v>57817</v>
+        <v>98443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -955,13 +954,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578460</v>
+        <v>578475</v>
       </c>
       <c r="R4" t="n">
-        <v>6406044</v>
+        <v>6406034</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,6 +998,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33687-2025 artfynd.xlsx
+++ b/artfynd/A 33687-2025 artfynd.xlsx
@@ -794,46 +794,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127111075</v>
+        <v>127110780</v>
       </c>
       <c r="B3" t="n">
-        <v>57817</v>
+        <v>98443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -841,13 +845,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578460</v>
+        <v>578475</v>
       </c>
       <c r="R3" t="n">
-        <v>6406044</v>
+        <v>6406034</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,6 +889,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -903,50 +908,46 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127110780</v>
+        <v>127111075</v>
       </c>
       <c r="B4" t="n">
-        <v>98443</v>
+        <v>57817</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -954,13 +955,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578475</v>
+        <v>578460</v>
       </c>
       <c r="R4" t="n">
-        <v>6406034</v>
+        <v>6406044</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -998,7 +999,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33687-2025 artfynd.xlsx
+++ b/artfynd/A 33687-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127110801</v>
       </c>
       <c r="B2" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,50 +794,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127110780</v>
+        <v>127111075</v>
       </c>
       <c r="B3" t="n">
-        <v>98443</v>
+        <v>57821</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -845,13 +841,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578475</v>
+        <v>578460</v>
       </c>
       <c r="R3" t="n">
-        <v>6406034</v>
+        <v>6406044</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -889,7 +885,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -908,46 +903,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127111075</v>
+        <v>127110780</v>
       </c>
       <c r="B4" t="n">
-        <v>57817</v>
+        <v>98447</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -955,13 +954,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578460</v>
+        <v>578475</v>
       </c>
       <c r="R4" t="n">
-        <v>6406044</v>
+        <v>6406034</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,6 +998,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1020,7 +1020,7 @@
         <v>127110856</v>
       </c>
       <c r="B5" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>127110820</v>
       </c>
       <c r="B6" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 33687-2025 artfynd.xlsx
+++ b/artfynd/A 33687-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127110801</v>
       </c>
       <c r="B2" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>127110780</v>
       </c>
       <c r="B4" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>127110856</v>
       </c>
       <c r="B5" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>127110820</v>
       </c>
       <c r="B6" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 33687-2025 artfynd.xlsx
+++ b/artfynd/A 33687-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127110801</v>
       </c>
       <c r="B2" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>127111075</v>
       </c>
       <c r="B3" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>127110780</v>
       </c>
       <c r="B4" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>127110856</v>
       </c>
       <c r="B5" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>127110820</v>
       </c>
       <c r="B6" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 33687-2025 artfynd.xlsx
+++ b/artfynd/A 33687-2025 artfynd.xlsx
@@ -794,46 +794,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127111075</v>
+        <v>127110780</v>
       </c>
       <c r="B3" t="n">
-        <v>57823</v>
+        <v>98450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -841,13 +845,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578460</v>
+        <v>578475</v>
       </c>
       <c r="R3" t="n">
-        <v>6406044</v>
+        <v>6406034</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,6 +889,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -903,50 +908,46 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127110780</v>
+        <v>127111075</v>
       </c>
       <c r="B4" t="n">
-        <v>98450</v>
+        <v>57823</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -954,13 +955,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578475</v>
+        <v>578460</v>
       </c>
       <c r="R4" t="n">
-        <v>6406034</v>
+        <v>6406044</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -998,7 +999,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33687-2025 artfynd.xlsx
+++ b/artfynd/A 33687-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127110801</v>
       </c>
       <c r="B2" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>127110780</v>
       </c>
       <c r="B3" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>127110856</v>
       </c>
       <c r="B5" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>127110820</v>
       </c>
       <c r="B6" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 33687-2025 artfynd.xlsx
+++ b/artfynd/A 33687-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127110801</v>
       </c>
       <c r="B2" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>127110780</v>
       </c>
       <c r="B3" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>127111075</v>
       </c>
       <c r="B4" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>127110856</v>
       </c>
       <c r="B5" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>127110820</v>
       </c>
       <c r="B6" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 33687-2025 artfynd.xlsx
+++ b/artfynd/A 33687-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127110801</v>
       </c>
       <c r="B2" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,50 +794,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127110780</v>
+        <v>127111075</v>
       </c>
       <c r="B3" t="n">
-        <v>98459</v>
+        <v>57832</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -845,13 +841,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578475</v>
+        <v>578460</v>
       </c>
       <c r="R3" t="n">
-        <v>6406034</v>
+        <v>6406044</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -889,7 +885,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -908,46 +903,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127111075</v>
+        <v>127110780</v>
       </c>
       <c r="B4" t="n">
-        <v>57826</v>
+        <v>98467</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -955,13 +954,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578460</v>
+        <v>578475</v>
       </c>
       <c r="R4" t="n">
-        <v>6406044</v>
+        <v>6406034</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,6 +998,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1020,7 +1020,7 @@
         <v>127110856</v>
       </c>
       <c r="B5" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>127110820</v>
       </c>
       <c r="B6" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 33687-2025 artfynd.xlsx
+++ b/artfynd/A 33687-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127110801</v>
       </c>
       <c r="B2" t="n">
-        <v>98467</v>
+        <v>98436</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>127111075</v>
       </c>
       <c r="B3" t="n">
-        <v>57832</v>
+        <v>57817</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>127110780</v>
       </c>
       <c r="B4" t="n">
-        <v>98467</v>
+        <v>98436</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>127110856</v>
       </c>
       <c r="B5" t="n">
-        <v>98467</v>
+        <v>98436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>127110820</v>
       </c>
       <c r="B6" t="n">
-        <v>98467</v>
+        <v>98436</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 33687-2025 artfynd.xlsx
+++ b/artfynd/A 33687-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127110801</v>
       </c>
       <c r="B2" t="n">
-        <v>98436</v>
+        <v>98467</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>127111075</v>
       </c>
       <c r="B3" t="n">
-        <v>57817</v>
+        <v>57832</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>127110780</v>
       </c>
       <c r="B4" t="n">
-        <v>98436</v>
+        <v>98467</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>127110856</v>
       </c>
       <c r="B5" t="n">
-        <v>98436</v>
+        <v>98467</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>127110820</v>
       </c>
       <c r="B6" t="n">
-        <v>98436</v>
+        <v>98467</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
